--- a/artfynd/A 39505-2026 artfynd.xlsx
+++ b/artfynd/A 39505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137408014</v>
       </c>
       <c r="B2" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137408025</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137408026</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137408028</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137408017</v>
       </c>
       <c r="B6" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137408018</v>
       </c>
       <c r="B7" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137408021</v>
       </c>
       <c r="B11" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137408022</v>
       </c>
       <c r="B12" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>137408023</v>
       </c>
       <c r="B13" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>137408013</v>
       </c>
       <c r="B14" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137408011</v>
       </c>
       <c r="B15" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>137408016</v>
       </c>
       <c r="B16" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137408024</v>
       </c>
       <c r="B17" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>137408027</v>
       </c>
       <c r="B18" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>137408029</v>
       </c>
       <c r="B19" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39505-2026 artfynd.xlsx
+++ b/artfynd/A 39505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137408014</v>
       </c>
       <c r="B2" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137408025</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137408026</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137408028</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137408018</v>
       </c>
       <c r="B7" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137408021</v>
       </c>
       <c r="B11" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137408022</v>
       </c>
       <c r="B12" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>137408023</v>
       </c>
       <c r="B13" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>137408013</v>
       </c>
       <c r="B14" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137408011</v>
       </c>
       <c r="B15" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>137408016</v>
       </c>
       <c r="B16" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137408024</v>
       </c>
       <c r="B17" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>137408027</v>
       </c>
       <c r="B18" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>137408029</v>
       </c>
       <c r="B19" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39505-2026 artfynd.xlsx
+++ b/artfynd/A 39505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137408014</v>
       </c>
       <c r="B2" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137408025</v>
       </c>
       <c r="B3" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137408026</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137408028</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137408018</v>
       </c>
       <c r="B7" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137408021</v>
       </c>
       <c r="B11" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137408022</v>
       </c>
       <c r="B12" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>137408023</v>
       </c>
       <c r="B13" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>137408013</v>
       </c>
       <c r="B14" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137408011</v>
       </c>
       <c r="B15" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>137408016</v>
       </c>
       <c r="B16" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137408024</v>
       </c>
       <c r="B17" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>137408027</v>
       </c>
       <c r="B18" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>137408029</v>
       </c>
       <c r="B19" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 39505-2026 artfynd.xlsx
+++ b/artfynd/A 39505-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137408014</v>
       </c>
       <c r="B2" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137408025</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137408026</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137408028</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137408017</v>
       </c>
       <c r="B6" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137408018</v>
       </c>
       <c r="B7" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137408015</v>
       </c>
       <c r="B8" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>137408021</v>
       </c>
       <c r="B11" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>137408022</v>
       </c>
       <c r="B12" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>137408023</v>
       </c>
       <c r="B13" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>137408013</v>
       </c>
       <c r="B14" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>137408011</v>
       </c>
       <c r="B15" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>137408016</v>
       </c>
       <c r="B16" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>137408024</v>
       </c>
       <c r="B17" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>137408027</v>
       </c>
       <c r="B18" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>137408029</v>
       </c>
       <c r="B19" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
